--- a/3курс/Лабораторные/Архитектура ЭВМ/2/2lab.xlsx
+++ b/3курс/Лабораторные/Архитектура ЭВМ/2/2lab.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\repos\Облако\ВУЗ\3курс\Лабораторные\Архитектура ЭВМ\2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Vyz\3курс\Лабораторные\Архитектура ЭВМ\2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B78F2A0-6FE5-4741-B019-2C610BC373B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572E507C-B4DE-463D-9921-4E45C43B9DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{33F9B2C4-F068-4C42-B129-2D0398F4D904}"/>
+    <workbookView xWindow="-108" yWindow="372" windowWidth="23256" windowHeight="14136" xr2:uid="{33F9B2C4-F068-4C42-B129-2D0398F4D904}"/>
   </bookViews>
   <sheets>
     <sheet name="лаба1" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>+1</t>
+    <t>LS2: "A ∨ B"</t>
   </si>
   <si>
-    <t>LS2: "A ∨ B"</t>
+    <t>LS1 "Y/2"</t>
+  </si>
+  <si>
+    <t>ы</t>
   </si>
 </sst>
 </file>
@@ -172,8 +175,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="673113" y="200460"/>
-          <a:ext cx="15587423" cy="9208578"/>
+          <a:off x="674814" y="202161"/>
+          <a:ext cx="15532995" cy="9237494"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -214,6 +217,715 @@
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData fPrintsWithSheet="0"/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>318189</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>307146</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>70403</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rectangle 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEC54EEA-6B3F-5CBD-D09C-F54564EF9BA5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14403283" y="3167064"/>
+          <a:ext cx="655707" cy="2415933"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>200967</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>114122</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>410307</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>31843</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A52CCDA6-0375-393A-3C2E-CB8BF44A45D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="11187415" y="5293447"/>
+          <a:ext cx="696110" cy="170205"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>523009</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>30569</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>91629</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Rectangle 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FED18B42-13D8-CDBC-9FBE-1CB0A3E43C83}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9940853" y="1661725"/>
+          <a:ext cx="4436341" cy="1061185"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>69273</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>11545</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>184727</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>138545</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Oval 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96C127BA-1BBD-006B-071B-2468E45E601F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6627091" y="1431636"/>
+          <a:ext cx="115454" cy="127000"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="Straight Connector 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0C15D78-91C6-B098-95C5-569912B14454}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="12092940" y="1859280"/>
+          <a:ext cx="7620" cy="746760"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>167819</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>119946</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>205149</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>30569</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="Straight Connector 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6C6C0D5-CFB5-4D70-AD81-D46196153E2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="6" idx="5"/>
+          <a:endCxn id="5" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6704350" y="1572509"/>
+          <a:ext cx="5454674" cy="89216"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>30569</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>205625</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>288133</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="Straight Connector 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C52FE96-17E4-C12E-5733-72290A8CD088}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="5" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="12113895" y="1661725"/>
+          <a:ext cx="45605" cy="388533"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Rectangle 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB8750E2-6DF2-8329-23BA-5C9F815C5C06}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6362700" y="601980"/>
+          <a:ext cx="228600" cy="198120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100"/>
+            <a:t>Н</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>101495</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>35719</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>90452</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>353772</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Rectangle 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73CC7C31-8B76-417B-BF6B-5D343F33679F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="1495619">
+          <a:off x="14186589" y="5548313"/>
+          <a:ext cx="655707" cy="318053"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>166688</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>166687</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Rectangle 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0558C2D1-E68A-F295-3E6D-DB5D7446F7FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15370969" y="2976563"/>
+          <a:ext cx="881062" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>358588</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>64035</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>12807</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>51227</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="TextBox 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{563715CB-39BA-A48C-5808-F4ECFBAE5260}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6038370" y="621127"/>
+          <a:ext cx="531479" cy="505865"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="2800"/>
+            <a:t>Y</a:t>
+          </a:r>
+          <a:endParaRPr lang="ru-RU" sz="2800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
@@ -536,46 +1248,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89623F24-D8F7-4BDE-85F3-835114F5308D}">
   <dimension ref="A2:AG114"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.59765625" style="2" customWidth="1"/>
     <col min="2" max="2" width="5.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="6.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="5.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.69921875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="5.19921875" style="2" customWidth="1"/>
     <col min="5" max="5" width="5" style="2" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="2" customWidth="1"/>
-    <col min="7" max="9" width="6.625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="3.625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="6.125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="6.375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="5.875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="5.625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="6.75" style="2" customWidth="1"/>
-    <col min="16" max="16" width="7.125" style="2" customWidth="1"/>
+    <col min="7" max="9" width="6.59765625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="3.59765625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="6.09765625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.3984375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="5.8984375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="5.59765625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="6.69921875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="7.09765625" style="2" customWidth="1"/>
     <col min="17" max="17" width="7" style="2" customWidth="1"/>
-    <col min="18" max="18" width="4.875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="4.8984375" style="2" customWidth="1"/>
     <col min="19" max="19" width="6" style="2" customWidth="1"/>
-    <col min="20" max="20" width="6.25" style="2" customWidth="1"/>
-    <col min="21" max="21" width="7.625" style="2" customWidth="1"/>
-    <col min="22" max="28" width="6.375" style="2" customWidth="1"/>
-    <col min="29" max="16384" width="8.75" style="2"/>
+    <col min="20" max="20" width="6.19921875" style="2" customWidth="1"/>
+    <col min="21" max="21" width="7.59765625" style="2" customWidth="1"/>
+    <col min="22" max="28" width="6.3984375" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="8.69921875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:32" ht="30" customHeight="1">
+    <row r="2" spans="2:32" ht="30" customHeight="1">
       <c r="B2" s="2">
         <v>0</v>
       </c>
       <c r="C2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
         <v>1</v>
@@ -587,10 +1299,10 @@
         <v>1</v>
       </c>
       <c r="K2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2">
         <v>0</v>
@@ -605,14 +1317,14 @@
         <v>0</v>
       </c>
       <c r="Q2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="10.5" customHeight="1"/>
-    <row r="10" spans="1:32" ht="26.25" customHeight="1">
+    <row r="9" spans="2:32" ht="10.5" customHeight="1"/>
+    <row r="10" spans="2:32" ht="26.25" customHeight="1">
       <c r="O10" s="3"/>
       <c r="V10" s="2">
         <v>0</v>
@@ -624,27 +1336,27 @@
         <v>0</v>
       </c>
       <c r="Y10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="2">
         <v>0</v>
       </c>
       <c r="AB10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32">
-      <c r="A15" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:32">
+      <c r="AF15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:32">
       <c r="AF16" s="1">
         <v>1</v>
       </c>
@@ -652,7 +1364,7 @@
     <row r="18" spans="4:33" ht="24.75" customHeight="1">
       <c r="F18" s="2">
         <f>D114</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2">
         <f>D110</f>
@@ -685,50 +1397,68 @@
     </row>
     <row r="19" spans="4:33">
       <c r="S19" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:33">
+      <c r="S20" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="4:33">
       <c r="D26" s="5">
         <f>IF(_xlfn.XOR(E113,E109),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="4:33">
       <c r="D27" s="5"/>
     </row>
-    <row r="29" spans="4:33" ht="6" customHeight="1"/>
+    <row r="28" spans="4:33">
+      <c r="Z28" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="5"/>
+      <c r="AB28" s="5"/>
+      <c r="AC28" s="5"/>
+    </row>
+    <row r="29" spans="4:33" ht="6" customHeight="1">
+      <c r="Z29" s="5"/>
+      <c r="AA29" s="5"/>
+      <c r="AB29" s="5"/>
+      <c r="AC29" s="5"/>
+    </row>
     <row r="30" spans="4:33" ht="34.5" customHeight="1">
       <c r="V30" s="2">
-        <f>IF(AF16,IF(лаба1!AG31,AC10,V10),0)</f>
+        <f>IF(AG31,IF(лаба1!AG31,R2,K2),0)</f>
         <v>1</v>
       </c>
       <c r="W30" s="2">
-        <f>IF(AF16,IF(лаба1!AG31,V10,W10),0)</f>
-        <v>0</v>
+        <f>IF(AG31,IF(лаба1!AG31,K2,L2),0)</f>
+        <v>1</v>
       </c>
       <c r="X30" s="2">
-        <f>IF(AF16,IF(лаба1!AG31,W10,X10),0)</f>
-        <v>0</v>
+        <f>IF(AG31,IF(лаба1!AG31,L2,M2),0)</f>
+        <v>1</v>
       </c>
       <c r="Y30" s="2">
-        <f>IF(AF16,IF(лаба1!AG31,X10,Y10),0)</f>
+        <f>IF(AG31,IF(лаба1!AG31,M2,N2),0)</f>
         <v>0</v>
       </c>
       <c r="Z30" s="2">
-        <f>IF(AF16,IF(AG31,Y10,Z10),0)</f>
-        <v>1</v>
+        <f>IF(AG31,IF(AG31,N2,O2),0)</f>
+        <v>0</v>
       </c>
       <c r="AA30" s="2">
-        <f>IF(AF16,IF(лаба1!AG31,Z10,AA10),0)</f>
-        <v>1</v>
+        <f>IF(AG31,IF(лаба1!AG31,O2,P2),0)</f>
+        <v>0</v>
       </c>
       <c r="AB30" s="2">
-        <f>IF(AF16,IF(лаба1!AG31,AA10,AB10),0)</f>
+        <f>IF(AG31,IF(лаба1!AG31,P2,Q2),0)</f>
         <v>0</v>
       </c>
       <c r="AC30" s="2">
-        <f>IF(AF16,IF(лаба1!AG31,AB10,AC10),0)</f>
+        <f>IF(AG31,IF(лаба1!AG31,Q2,R2),0)</f>
         <v>1</v>
       </c>
     </row>
@@ -737,9 +1467,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="11:22" ht="27">
+    <row r="36" spans="11:22" ht="27.6">
       <c r="N36" s="6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" s="6"/>
       <c r="P36" s="6"/>
@@ -764,11 +1494,11 @@
       </c>
       <c r="O48" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P48" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="2">
         <f t="shared" si="0"/>
@@ -776,11 +1506,11 @@
       </c>
       <c r="R48" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" s="2">
         <f t="shared" si="0"/>
@@ -792,14 +1522,7 @@
       </c>
     </row>
     <row r="78" spans="2:2">
-      <c r="B78" s="4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:2">
-      <c r="B79" s="2">
-        <v>0</v>
-      </c>
+      <c r="B78" s="4"/>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
@@ -807,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="C82" s="2">
-        <f>IF(AND(B79,A82),1,0)</f>
+        <f>IF(AND(AF15,A82),1,0)</f>
         <v>0</v>
       </c>
       <c r="E82" s="2">
@@ -821,18 +1544,18 @@
         <v>1</v>
       </c>
       <c r="D83" s="2">
-        <f>IF(AND(S19,AF16),IF(_xlfn.XOR(B79,A82),1,0),0)</f>
+        <f>IF(AND(S19,AF16),IF(_xlfn.XOR(AF15,A82),1,0),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
         <f>IF(_xlfn.XOR(H2,Q2),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C87" s="2">
         <f>IF(AND(E82,A87),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" s="2">
         <f>IF(OR(A88,C87),1,0)</f>
@@ -842,7 +1565,7 @@
     <row r="88" spans="1:5">
       <c r="A88" s="2">
         <f>IF(AND(H2,Q2),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88" s="2">
         <f>IF(AND(S19,AF16),IF(_xlfn.XOR(E82,A87),1,0),0)</f>
@@ -876,15 +1599,15 @@
     <row r="96" spans="1:5">
       <c r="A96" s="2">
         <f>IF(_xlfn.XOR(F2,O2),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C96" s="2">
         <f>IF(AND(E91,A96),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" s="2">
         <f>IF(OR(A97,C96),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -900,15 +1623,15 @@
     <row r="100" spans="1:5">
       <c r="A100" s="2">
         <f>IF(_xlfn.XOR(E2,N2),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C100" s="2">
         <f>IF(AND(E96,A100),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" s="2">
         <f>IF(OR(A101,C100),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -924,15 +1647,15 @@
     <row r="105" spans="1:5">
       <c r="A105" s="2">
         <f>IF(_xlfn.XOR(D2,M2),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C105" s="2">
         <f>IF(AND(E100,A105),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" s="2">
         <f>IF(OR(A106,C105),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -952,11 +1675,11 @@
       </c>
       <c r="C109" s="2">
         <f>IF(AND(E105,A109),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E109" s="2">
         <f>IF(OR(A110,C109),1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -972,7 +1695,7 @@
     <row r="113" spans="1:5">
       <c r="A113" s="2">
         <f>IF(_xlfn.XOR(B2,K2),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C113" s="2">
         <f>IF(AND(E109,A113),1,0)</f>
@@ -990,13 +1713,14 @@
       </c>
       <c r="D114" s="2">
         <f>IF(AND(S19,AF16),IF(_xlfn.XOR(E109,A113),1,0),0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="D26:D27"/>
     <mergeCell ref="N36:V36"/>
+    <mergeCell ref="Z28:AC29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
